--- a/Result/profitability/2601.xlsx
+++ b/Result/profitability/2601.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02250000000000002</v>
+        <v>0.00874999999999998</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -778,7 +778,7 @@
         <v>2.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3225</v>
+        <v>0.325</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -895,7 +895,7 @@
         <v>2.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -1012,7 +1012,7 @@
         <v>2.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9875</v>
+        <v>0.9762500000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1129,7 +1129,7 @@
         <v>1.19</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1475</v>
+        <v>1.13625</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1254,9 +1254,11 @@
         <v>0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>1.23875</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>1.3775</v>
+      </c>
+      <c r="N7" t="n">
+        <v>25.7675</v>
+      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -1379,10 +1381,10 @@
         <v>1.03</v>
       </c>
       <c r="M8" t="n">
-        <v>1.52875</v>
+        <v>1.50875</v>
       </c>
       <c r="N8" t="n">
-        <v>26.15625</v>
+        <v>24.935</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2014,7 +2016,7 @@
         <v>1.13</v>
       </c>
       <c r="M13" t="n">
-        <v>0.99875</v>
+        <v>0.9987499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>23.61875</v>
@@ -9810,6 +9812,131 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2601</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>407</v>
+      </c>
+      <c r="D75" t="n">
+        <v>337</v>
+      </c>
+      <c r="E75" t="n">
+        <v>70</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>38</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-195</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-156</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-150</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.2625</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3625231910946196</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-42.91</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.7140955233815943</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
